--- a/xlsx/Power/p4.xlsx
+++ b/xlsx/Power/p4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894F2D2A-4444-4955-BA90-988C4AE39B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B03161-51B3-406F-AB2B-5CA7C3FD9E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C14B83D0-DCE4-40D4-8D7A-2DCF62E7D001}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C14B83D0-DCE4-40D4-8D7A-2DCF62E7D001}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.251</v>
       </c>
       <c r="C1">
-        <v>0.374</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="D1">
-        <v>0.45200000000000001</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="E1">
-        <v>0.51900000000000002</v>
+        <v>0.29199999999999998</v>
       </c>
       <c r="F1">
-        <v>0.57099999999999995</v>
+        <v>0.379</v>
       </c>
       <c r="G1">
-        <v>0.66500000000000004</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="H1">
-        <v>0.69599999999999995</v>
+        <v>0.56299999999999994</v>
       </c>
       <c r="I1">
-        <v>0.76</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="J1">
-        <v>0.78100000000000003</v>
+        <v>0.68500000000000005</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="C2">
-        <v>0.441</v>
+        <v>8.6999999999999994E-2</v>
       </c>
       <c r="D2">
-        <v>0.50900000000000001</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="E2">
-        <v>0.58399999999999996</v>
+        <v>0.35</v>
       </c>
       <c r="F2">
-        <v>0.65900000000000003</v>
+        <v>0.45700000000000002</v>
       </c>
       <c r="G2">
-        <v>0.72899999999999998</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="H2">
-        <v>0.76200000000000001</v>
+        <v>0.63200000000000001</v>
       </c>
       <c r="I2">
-        <v>0.80100000000000005</v>
+        <v>0.71</v>
       </c>
       <c r="J2">
-        <v>0.82599999999999996</v>
+        <v>0.745</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,60 +468,60 @@
         <v>0.26</v>
       </c>
       <c r="C3">
-        <v>0.379</v>
+        <v>0.434</v>
       </c>
       <c r="D3">
-        <v>0.47</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="E3">
-        <v>0.53700000000000003</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="F3">
-        <v>0.60399999999999998</v>
+        <v>0.61399999999999999</v>
       </c>
       <c r="G3">
         <v>0.67700000000000005</v>
       </c>
       <c r="H3">
-        <v>0.73299999999999998</v>
+        <v>0.73399999999999999</v>
       </c>
       <c r="I3">
-        <v>0.78300000000000003</v>
+        <v>0.78400000000000003</v>
       </c>
       <c r="J3">
-        <v>0.81</v>
+        <v>0.81299999999999994</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.16400000000000001</v>
+        <v>0.187</v>
       </c>
       <c r="B4">
-        <v>0.23899999999999999</v>
+        <v>0.247</v>
       </c>
       <c r="C4">
-        <v>0.373</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="D4">
-        <v>0.46200000000000002</v>
+        <v>0.45900000000000002</v>
       </c>
       <c r="E4">
         <v>0.52400000000000002</v>
       </c>
       <c r="F4">
-        <v>0.6</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="G4">
         <v>0.66400000000000003</v>
       </c>
       <c r="H4">
-        <v>0.71699999999999997</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="I4">
-        <v>0.77500000000000002</v>
+        <v>0.77400000000000002</v>
       </c>
       <c r="J4">
-        <v>0.81200000000000006</v>
+        <v>0.81599999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="C5">
-        <v>8.5000000000000006E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0.113</v>
+        <v>2E-3</v>
       </c>
       <c r="E5">
-        <v>0.129</v>
+        <v>1.7999999999999999E-2</v>
       </c>
       <c r="F5">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="G5">
-        <v>0.191</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="H5">
-        <v>0.191</v>
+        <v>6.6000000000000003E-2</v>
       </c>
       <c r="I5">
-        <v>0.23200000000000001</v>
+        <v>9.4E-2</v>
       </c>
       <c r="J5">
-        <v>0.27</v>
+        <v>0.13500000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="C6">
-        <v>0.42</v>
+        <v>0.55400000000000005</v>
       </c>
       <c r="D6">
-        <v>0.48</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="E6">
-        <v>0.54500000000000004</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="F6">
-        <v>0.61799999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="G6">
-        <v>0.69799999999999995</v>
+        <v>0.70599999999999996</v>
       </c>
       <c r="H6">
-        <v>0.71499999999999997</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="I6">
-        <v>0.752</v>
+        <v>0.75800000000000001</v>
       </c>
       <c r="J6">
-        <v>0.78300000000000003</v>
+        <v>0.79300000000000004</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="C7">
-        <v>0.373</v>
+        <v>0.36799999999999999</v>
       </c>
       <c r="D7">
-        <v>0.433</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="E7">
-        <v>0.47799999999999998</v>
+        <v>0.48099999999999998</v>
       </c>
       <c r="F7">
-        <v>0.53600000000000003</v>
+        <v>0.53300000000000003</v>
       </c>
       <c r="G7">
-        <v>0.61</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="H7">
         <v>0.63100000000000001</v>
       </c>
       <c r="I7">
-        <v>0.68100000000000005</v>
+        <v>0.67400000000000004</v>
       </c>
       <c r="J7">
-        <v>0.71599999999999997</v>
+        <v>0.71199999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.111</v>
       </c>
       <c r="C8">
-        <v>0.16800000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.23899999999999999</v>
+        <v>3.5999999999999997E-2</v>
       </c>
       <c r="E8">
-        <v>0.28799999999999998</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="F8">
-        <v>0.3</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="G8">
-        <v>0.36899999999999999</v>
+        <v>0.20899999999999999</v>
       </c>
       <c r="H8">
-        <v>0.40600000000000003</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="I8">
-        <v>0.503</v>
+        <v>0.111</v>
       </c>
       <c r="J8">
-        <v>0.52500000000000002</v>
+        <v>0.14199999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.129</v>
       </c>
       <c r="C9">
-        <v>0.39400000000000002</v>
+        <v>0.65500000000000003</v>
       </c>
       <c r="D9">
-        <v>0.251</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="E9">
-        <v>0.23</v>
+        <v>0.746</v>
       </c>
       <c r="F9">
-        <v>0.21299999999999999</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="G9">
-        <v>0.247</v>
+        <v>0.318</v>
       </c>
       <c r="H9">
-        <v>0.26600000000000001</v>
+        <v>0.313</v>
       </c>
       <c r="I9">
-        <v>0.317</v>
+        <v>0.36</v>
       </c>
       <c r="J9">
-        <v>0.34100000000000003</v>
+        <v>0.36799999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p4.xlsx
+++ b/xlsx/Power/p4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B03161-51B3-406F-AB2B-5CA7C3FD9E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13868986-E89D-4987-BB0E-2256F2E5F56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C14B83D0-DCE4-40D4-8D7A-2DCF62E7D001}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C14B83D0-DCE4-40D4-8D7A-2DCF62E7D001}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.251</v>
       </c>
       <c r="C1">
-        <v>5.7000000000000002E-2</v>
+        <v>0.374</v>
       </c>
       <c r="D1">
-        <v>0.17899999999999999</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="E1">
-        <v>0.29199999999999998</v>
+        <v>0.51900000000000002</v>
       </c>
       <c r="F1">
-        <v>0.379</v>
+        <v>0.57099999999999995</v>
       </c>
       <c r="G1">
-        <v>0.47499999999999998</v>
+        <v>0.66500000000000004</v>
       </c>
       <c r="H1">
-        <v>0.56299999999999994</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="I1">
-        <v>0.64400000000000002</v>
+        <v>0.76</v>
       </c>
       <c r="J1">
-        <v>0.68500000000000005</v>
+        <v>0.78200000000000003</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,92 +436,92 @@
         <v>0.30599999999999999</v>
       </c>
       <c r="C2">
-        <v>8.6999999999999994E-2</v>
+        <v>0.441</v>
       </c>
       <c r="D2">
-        <v>0.24399999999999999</v>
+        <v>0.50900000000000001</v>
       </c>
       <c r="E2">
-        <v>0.35</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F2">
-        <v>0.45700000000000002</v>
+        <v>0.66</v>
       </c>
       <c r="G2">
-        <v>0.56000000000000005</v>
+        <v>0.72899999999999998</v>
       </c>
       <c r="H2">
-        <v>0.63200000000000001</v>
+        <v>0.76200000000000001</v>
       </c>
       <c r="I2">
-        <v>0.71</v>
+        <v>0.80100000000000005</v>
       </c>
       <c r="J2">
-        <v>0.745</v>
+        <v>0.82599999999999996</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.16300000000000001</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="B3">
         <v>0.26</v>
       </c>
       <c r="C3">
-        <v>0.434</v>
+        <v>0.379</v>
       </c>
       <c r="D3">
-        <v>0.47799999999999998</v>
+        <v>0.47</v>
       </c>
       <c r="E3">
-        <v>0.54500000000000004</v>
+        <v>0.53700000000000003</v>
       </c>
       <c r="F3">
-        <v>0.61399999999999999</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="G3">
         <v>0.67700000000000005</v>
       </c>
       <c r="H3">
-        <v>0.73399999999999999</v>
+        <v>0.73299999999999998</v>
       </c>
       <c r="I3">
-        <v>0.78400000000000003</v>
+        <v>0.78300000000000003</v>
       </c>
       <c r="J3">
-        <v>0.81299999999999994</v>
+        <v>0.81</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.187</v>
+        <v>0.16400000000000001</v>
       </c>
       <c r="B4">
-        <v>0.247</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="C4">
-        <v>0.38200000000000001</v>
+        <v>0.373</v>
       </c>
       <c r="D4">
-        <v>0.45900000000000002</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="E4">
         <v>0.52400000000000002</v>
       </c>
       <c r="F4">
-        <v>0.60299999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="G4">
         <v>0.66400000000000003</v>
       </c>
       <c r="H4">
-        <v>0.71599999999999997</v>
+        <v>0.71699999999999997</v>
       </c>
       <c r="I4">
-        <v>0.77400000000000002</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="J4">
-        <v>0.81599999999999995</v>
+        <v>0.81200000000000006</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,28 +532,28 @@
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="D5">
-        <v>2E-3</v>
+        <v>0.113</v>
       </c>
       <c r="E5">
-        <v>1.7999999999999999E-2</v>
+        <v>0.129</v>
       </c>
       <c r="F5">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="G5">
-        <v>7.0000000000000007E-2</v>
+        <v>0.191</v>
       </c>
       <c r="H5">
-        <v>6.6000000000000003E-2</v>
+        <v>0.191</v>
       </c>
       <c r="I5">
-        <v>9.4E-2</v>
+        <v>0.23200000000000001</v>
       </c>
       <c r="J5">
-        <v>0.13500000000000001</v>
+        <v>0.26900000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -564,28 +564,28 @@
         <v>0.29199999999999998</v>
       </c>
       <c r="C6">
-        <v>0.55400000000000005</v>
+        <v>0.42</v>
       </c>
       <c r="D6">
-        <v>0.53300000000000003</v>
+        <v>0.48</v>
       </c>
       <c r="E6">
-        <v>0.57499999999999996</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="F6">
-        <v>0.63</v>
+        <v>0.61799999999999999</v>
       </c>
       <c r="G6">
-        <v>0.70599999999999996</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="H6">
-        <v>0.72299999999999998</v>
+        <v>0.71499999999999997</v>
       </c>
       <c r="I6">
-        <v>0.75800000000000001</v>
+        <v>0.752</v>
       </c>
       <c r="J6">
-        <v>0.79300000000000004</v>
+        <v>0.78300000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.27700000000000002</v>
       </c>
       <c r="C7">
-        <v>0.36799999999999999</v>
+        <v>0.373</v>
       </c>
       <c r="D7">
-        <v>0.42799999999999999</v>
+        <v>0.433</v>
       </c>
       <c r="E7">
-        <v>0.48099999999999998</v>
+        <v>0.47799999999999998</v>
       </c>
       <c r="F7">
-        <v>0.53300000000000003</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="G7">
-        <v>0.60399999999999998</v>
+        <v>0.61</v>
       </c>
       <c r="H7">
         <v>0.63100000000000001</v>
       </c>
       <c r="I7">
-        <v>0.67400000000000004</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="J7">
-        <v>0.71199999999999997</v>
+        <v>0.71599999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.111</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="D8">
-        <v>3.5999999999999997E-2</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="E8">
-        <v>9.6000000000000002E-2</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="F8">
-        <v>0.13100000000000001</v>
+        <v>0.3</v>
       </c>
       <c r="G8">
-        <v>0.20899999999999999</v>
+        <v>0.36899999999999999</v>
       </c>
       <c r="H8">
-        <v>0.26600000000000001</v>
+        <v>0.40600000000000003</v>
       </c>
       <c r="I8">
-        <v>0.111</v>
+        <v>0.503</v>
       </c>
       <c r="J8">
-        <v>0.14199999999999999</v>
+        <v>0.52500000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.129</v>
       </c>
       <c r="C9">
-        <v>0.65500000000000003</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="D9">
-        <v>0.94199999999999995</v>
+        <v>0.251</v>
       </c>
       <c r="E9">
-        <v>0.746</v>
+        <v>0.23</v>
       </c>
       <c r="F9">
-        <v>0.35899999999999999</v>
+        <v>0.21299999999999999</v>
       </c>
       <c r="G9">
-        <v>0.318</v>
+        <v>0.247</v>
       </c>
       <c r="H9">
-        <v>0.313</v>
+        <v>0.26600000000000001</v>
       </c>
       <c r="I9">
-        <v>0.36</v>
+        <v>0.317</v>
       </c>
       <c r="J9">
-        <v>0.36799999999999999</v>
+        <v>0.34100000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p4.xlsx
+++ b/xlsx/Power/p4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13868986-E89D-4987-BB0E-2256F2E5F56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817CC781-75B6-4AEB-BCE9-4BAB9063535E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C14B83D0-DCE4-40D4-8D7A-2DCF62E7D001}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{C14B83D0-DCE4-40D4-8D7A-2DCF62E7D001}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,19 +398,19 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.16</v>
+        <v>0.157</v>
       </c>
       <c r="B1">
-        <v>0.251</v>
+        <v>0.252</v>
       </c>
       <c r="C1">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="D1">
-        <v>0.45200000000000001</v>
+        <v>0.45300000000000001</v>
       </c>
       <c r="E1">
-        <v>0.51900000000000002</v>
+        <v>0.52</v>
       </c>
       <c r="F1">
         <v>0.57099999999999995</v>
@@ -422,18 +422,18 @@
         <v>0.69599999999999995</v>
       </c>
       <c r="I1">
-        <v>0.76</v>
+        <v>0.76100000000000001</v>
       </c>
       <c r="J1">
-        <v>0.78200000000000003</v>
+        <v>0.78500000000000003</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.18</v>
+        <v>0.17699999999999999</v>
       </c>
       <c r="B2">
-        <v>0.30599999999999999</v>
+        <v>0.309</v>
       </c>
       <c r="C2">
         <v>0.441</v>
@@ -445,13 +445,13 @@
         <v>0.58399999999999996</v>
       </c>
       <c r="F2">
-        <v>0.66</v>
+        <v>0.65700000000000003</v>
       </c>
       <c r="G2">
-        <v>0.72899999999999998</v>
+        <v>0.72499999999999998</v>
       </c>
       <c r="H2">
-        <v>0.76200000000000001</v>
+        <v>0.755</v>
       </c>
       <c r="I2">
         <v>0.80100000000000005</v>
@@ -462,162 +462,162 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.16400000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="B3">
         <v>0.26</v>
       </c>
       <c r="C3">
-        <v>0.379</v>
+        <v>0.38600000000000001</v>
       </c>
       <c r="D3">
         <v>0.47</v>
       </c>
       <c r="E3">
-        <v>0.53700000000000003</v>
+        <v>0.54500000000000004</v>
       </c>
       <c r="F3">
         <v>0.60399999999999998</v>
       </c>
       <c r="G3">
-        <v>0.67700000000000005</v>
+        <v>0.67800000000000005</v>
       </c>
       <c r="H3">
-        <v>0.73299999999999998</v>
+        <v>0.73699999999999999</v>
       </c>
       <c r="I3">
-        <v>0.78300000000000003</v>
+        <v>0.78600000000000003</v>
       </c>
       <c r="J3">
-        <v>0.81</v>
+        <v>0.81599999999999995</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.16400000000000001</v>
+        <v>0.16200000000000001</v>
       </c>
       <c r="B4">
-        <v>0.23899999999999999</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="C4">
-        <v>0.373</v>
+        <v>0.38</v>
       </c>
       <c r="D4">
-        <v>0.46200000000000002</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="E4">
-        <v>0.52400000000000002</v>
+        <v>0.52500000000000002</v>
       </c>
       <c r="F4">
-        <v>0.6</v>
+        <v>0.60299999999999998</v>
       </c>
       <c r="G4">
-        <v>0.66400000000000003</v>
+        <v>0.66700000000000004</v>
       </c>
       <c r="H4">
-        <v>0.71699999999999997</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="I4">
-        <v>0.77500000000000002</v>
+        <v>0.78</v>
       </c>
       <c r="J4">
-        <v>0.81200000000000006</v>
+        <v>0.82099999999999995</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>3.7999999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>6.6000000000000003E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="C5">
-        <v>8.5000000000000006E-2</v>
+        <v>8.9999999999999993E-3</v>
       </c>
       <c r="D5">
-        <v>0.113</v>
+        <v>2.1000000000000001E-2</v>
       </c>
       <c r="E5">
-        <v>0.129</v>
+        <v>2.7E-2</v>
       </c>
       <c r="F5">
-        <v>0.16</v>
+        <v>2.4E-2</v>
       </c>
       <c r="G5">
-        <v>0.191</v>
+        <v>4.7E-2</v>
       </c>
       <c r="H5">
-        <v>0.191</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="I5">
-        <v>0.23200000000000001</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="J5">
-        <v>0.26900000000000002</v>
+        <v>9.0999999999999998E-2</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.193</v>
+        <v>0.191</v>
       </c>
       <c r="B6">
         <v>0.29199999999999998</v>
       </c>
       <c r="C6">
-        <v>0.42</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="D6">
-        <v>0.48</v>
+        <v>0.47899999999999998</v>
       </c>
       <c r="E6">
-        <v>0.54500000000000004</v>
+        <v>0.54300000000000004</v>
       </c>
       <c r="F6">
-        <v>0.61799999999999999</v>
+        <v>0.61699999999999999</v>
       </c>
       <c r="G6">
-        <v>0.69799999999999995</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="H6">
-        <v>0.71499999999999997</v>
+        <v>0.71199999999999997</v>
       </c>
       <c r="I6">
-        <v>0.752</v>
+        <v>0.748</v>
       </c>
       <c r="J6">
-        <v>0.78300000000000003</v>
+        <v>0.78400000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.189</v>
+        <v>0.187</v>
       </c>
       <c r="B7">
-        <v>0.27700000000000002</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="C7">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="D7">
-        <v>0.433</v>
+        <v>0.42799999999999999</v>
       </c>
       <c r="E7">
         <v>0.47799999999999998</v>
       </c>
       <c r="F7">
-        <v>0.53600000000000003</v>
+        <v>0.53500000000000003</v>
       </c>
       <c r="G7">
-        <v>0.61</v>
+        <v>0.60799999999999998</v>
       </c>
       <c r="H7">
         <v>0.63100000000000001</v>
       </c>
       <c r="I7">
-        <v>0.68100000000000005</v>
+        <v>0.67900000000000005</v>
       </c>
       <c r="J7">
-        <v>0.71599999999999997</v>
+        <v>0.71499999999999997</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -634,54 +634,54 @@
         <v>0.23899999999999999</v>
       </c>
       <c r="E8">
-        <v>0.28799999999999998</v>
+        <v>0.29099999999999998</v>
       </c>
       <c r="F8">
-        <v>0.3</v>
+        <v>0.307</v>
       </c>
       <c r="G8">
         <v>0.36899999999999999</v>
       </c>
       <c r="H8">
-        <v>0.40600000000000003</v>
+        <v>0.40699999999999997</v>
       </c>
       <c r="I8">
-        <v>0.503</v>
+        <v>0.505</v>
       </c>
       <c r="J8">
-        <v>0.52500000000000002</v>
+        <v>0.52600000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.114</v>
+        <v>0.115</v>
       </c>
       <c r="B9">
-        <v>0.129</v>
+        <v>0.13300000000000001</v>
       </c>
       <c r="C9">
-        <v>0.39400000000000002</v>
+        <v>0.39600000000000002</v>
       </c>
       <c r="D9">
-        <v>0.251</v>
+        <v>0.252</v>
       </c>
       <c r="E9">
-        <v>0.23</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="F9">
-        <v>0.21299999999999999</v>
+        <v>0.215</v>
       </c>
       <c r="G9">
-        <v>0.247</v>
+        <v>0.24399999999999999</v>
       </c>
       <c r="H9">
-        <v>0.26600000000000001</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="I9">
-        <v>0.317</v>
+        <v>0.32400000000000001</v>
       </c>
       <c r="J9">
-        <v>0.34100000000000003</v>
+        <v>0.34899999999999998</v>
       </c>
     </row>
   </sheetData>
